--- a/dp4_oxime/DP4_Sarotti_ZoneB_paste_format.xlsx
+++ b/dp4_oxime/DP4_Sarotti_ZoneB_paste_format.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="41">
   <si>
     <t>Nuclei</t>
   </si>
@@ -73,6 +73,9 @@
     <t>Aromatic</t>
   </si>
   <si>
+    <t>Aromatic / pyrazole</t>
+  </si>
+  <si>
     <t>Aromatic CH</t>
   </si>
   <si>
@@ -116,9 +119,6 @@
   </si>
   <si>
     <t>C5</t>
-  </si>
-  <si>
-    <t>C3</t>
   </si>
   <si>
     <t>C10</t>
@@ -468,7 +468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -508,13 +508,13 @@
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2">
-        <v>29.92796666666666</v>
+        <v>29.927967</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H2">
         <v>29.77</v>
@@ -531,10 +531,10 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3">
-        <v>27.75243333333333</v>
+        <v>27.752433</v>
       </c>
       <c r="G3" t="s">
         <v>39</v>
@@ -554,13 +554,13 @@
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F4">
         <v>26.65465</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H4">
         <v>26.65</v>
@@ -580,13 +580,13 @@
         <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F5">
         <v>24.5065</v>
       </c>
       <c r="G5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H5">
         <v>23.941</v>
@@ -606,13 +606,13 @@
         <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6">
         <v>24.6019</v>
       </c>
       <c r="G6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H6">
         <v>24.4462</v>
@@ -632,13 +632,13 @@
         <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F7">
         <v>24.26725</v>
       </c>
       <c r="G7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H7">
         <v>23.8193</v>
@@ -658,13 +658,13 @@
         <v>15</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8">
         <v>23.9462</v>
       </c>
       <c r="G8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H8">
         <v>24.0887</v>
@@ -684,13 +684,13 @@
         <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F9">
         <v>42.2965</v>
       </c>
       <c r="G9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -707,13 +707,13 @@
         <v>17</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F10">
         <v>52.1827</v>
       </c>
       <c r="G10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -730,13 +730,13 @@
         <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F11">
         <v>58.1784</v>
       </c>
       <c r="G11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -747,19 +747,19 @@
         <v>10</v>
       </c>
       <c r="C12">
-        <v>131.33</v>
+        <v>127.68</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F12">
         <v>62.9938</v>
       </c>
       <c r="G12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -770,19 +770,19 @@
         <v>10</v>
       </c>
       <c r="C13">
-        <v>127.68</v>
+        <v>127.43</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F13">
         <v>65.7726</v>
       </c>
       <c r="G13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -793,19 +793,19 @@
         <v>10</v>
       </c>
       <c r="C14">
-        <v>127.43</v>
+        <v>126.84</v>
       </c>
       <c r="D14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F14">
         <v>66.8511</v>
       </c>
       <c r="G14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -816,42 +816,39 @@
         <v>10</v>
       </c>
       <c r="C15">
-        <v>126.84</v>
+        <v>115.74</v>
       </c>
       <c r="D15" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F15">
-        <v>68.43300000000001</v>
+        <v>74.7594</v>
       </c>
       <c r="G15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>9</v>
       </c>
-      <c r="B16" t="s">
-        <v>10</v>
-      </c>
       <c r="C16">
-        <v>115.74</v>
+        <v>61.65</v>
       </c>
       <c r="D16" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F16">
-        <v>74.7594</v>
+        <v>130.8007</v>
       </c>
       <c r="G16" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -859,19 +856,19 @@
         <v>9</v>
       </c>
       <c r="C17">
-        <v>61.65</v>
+        <v>44.63</v>
       </c>
       <c r="D17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F17">
-        <v>130.8007</v>
+        <v>135.9479</v>
       </c>
       <c r="G17" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -879,38 +876,18 @@
         <v>9</v>
       </c>
       <c r="C18">
-        <v>44.63</v>
+        <v>7.85</v>
       </c>
       <c r="D18" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F18">
-        <v>135.9479</v>
+        <v>181.286</v>
       </c>
       <c r="G18" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19">
-        <v>7.85</v>
-      </c>
-      <c r="D19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" t="s">
-        <v>38</v>
-      </c>
-      <c r="F19">
-        <v>181.286</v>
-      </c>
-      <c r="G19" t="s">
         <v>38</v>
       </c>
     </row>
